--- a/artfynd/A 15523-2026 artfynd.xlsx
+++ b/artfynd/A 15523-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>91118149</v>
       </c>
       <c r="B2" t="n">
-        <v>6206</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -729,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488411.89144769</v>
+        <v>488412</v>
       </c>
       <c r="R2" t="n">
-        <v>6569432.828053401</v>
+        <v>6569433</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -762,19 +757,9 @@
           <t>2018-05-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -814,12 +799,7 @@
         <v>91114309</v>
       </c>
       <c r="B3" t="n">
-        <v>6202</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -870,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488411.89144769</v>
+        <v>488412</v>
       </c>
       <c r="R3" t="n">
-        <v>6569432.828053401</v>
+        <v>6569433</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -903,19 +883,9 @@
           <t>2018-05-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2018-06-23</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
